--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484141_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484141_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5813</v>
+        <v>5.0849</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5402</v>
+        <v>6.6049</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9589</v>
+        <v>-1.5201</v>
       </c>
       <c r="G2" t="n">
         <v>2.8072</v>
@@ -610,13 +610,13 @@
         <v>2.1822</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3693</v>
+        <v>0.8729</v>
       </c>
       <c r="T2" t="n">
-        <v>1.746</v>
+        <v>0.8107</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6233</v>
+        <v>0.0622</v>
       </c>
       <c r="V2" t="n">
         <v>1.2065</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6264</v>
+        <v>3.3532</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9006</v>
+        <v>2.5151</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7259</v>
+        <v>0.8381</v>
       </c>
       <c r="G3" t="n">
         <v>1.1912</v>
@@ -688,13 +688,13 @@
         <v>0.5952</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2368</v>
+        <v>0.9636</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1224</v>
+        <v>0.7369</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1145</v>
+        <v>0.2267</v>
       </c>
       <c r="V3" t="n">
         <v>0.6032</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6694</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2925</v>
+        <v>1.2529</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6232</v>
+        <v>-0.4268</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3506</v>
@@ -766,13 +766,13 @@
         <v>1.5871</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1071</v>
+        <v>0.0496</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1304</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2375</v>
+        <v>-0.0412</v>
       </c>
       <c r="V4" t="n">
         <v>0.532</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.028</v>
+        <v>-1.2983</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0575</v>
+        <v>-0.1595</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9705</v>
+        <v>-1.1388</v>
       </c>
       <c r="G5" t="n">
         <v>0.1774</v>
@@ -844,13 +844,13 @@
         <v>1.1903</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7947</v>
+        <v>0.5243</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5555</v>
+        <v>0.4535</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2392</v>
+        <v>0.0708</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2065</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3882</v>
+        <v>-1.3321</v>
       </c>
       <c r="E6" t="n">
         <v>-0.0864</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3018</v>
+        <v>-1.2457</v>
       </c>
       <c r="G6" t="n">
         <v>-0.8305</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5577</v>
+        <v>-0.5016</v>
       </c>
       <c r="T6" t="n">
         <v>-0.187</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3707</v>
+        <v>-0.3146</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0268</v>
+        <v>-1.5593</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8734</v>
+        <v>2.0604</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.9002</v>
+        <v>-3.6197</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6682</v>
@@ -1000,13 +1000,13 @@
         <v>1.1903</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8105</v>
+        <v>-0.3429</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0452</v>
+        <v>0.1418</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7652</v>
+        <v>-0.4847</v>
       </c>
       <c r="V7" t="n">
         <v>-1.7384</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3768</v>
+        <v>-2.0504</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.9728</v>
+        <v>-2.8707</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5959</v>
+        <v>0.8204</v>
       </c>
       <c r="G8" t="n">
         <v>-1.5398</v>
@@ -1078,13 +1078,13 @@
         <v>1.7855</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0873</v>
+        <v>0.4138</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3061</v>
+        <v>0.4082</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2188</v>
+        <v>0.0056</v>
       </c>
       <c r="V8" t="n">
         <v>0.266</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.4975</v>
+        <v>-3.7964</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8892</v>
+        <v>-1.3564</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.6083</v>
+        <v>-2.4399</v>
       </c>
       <c r="G9" t="n">
         <v>0.7628</v>
@@ -1156,13 +1156,13 @@
         <v>1.1903</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2765</v>
+        <v>-0.5753</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.255</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4887</v>
+        <v>-0.3203</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2065</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.227</v>
+        <v>-4.3408</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5408</v>
+        <v>-3.4582</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6863</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>-4.7414</v>
@@ -1234,13 +1234,13 @@
         <v>2.579</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3747</v>
+        <v>0.5115</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4988</v>
+        <v>0.5839</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1241</v>
+        <v>-0.0723</v>
       </c>
       <c r="V10" t="n">
         <v>1.2777</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.0412</v>
+        <v>-7.6603</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.6515</v>
+        <v>-8.1584</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.4982</v>
       </c>
       <c r="G11" t="n">
         <v>-6.1602</v>
@@ -1312,13 +1312,13 @@
         <v>2.579</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3696</v>
+        <v>0.0113</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.357</v>
+        <v>0.1361</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0126</v>
+        <v>-0.1248</v>
       </c>
       <c r="V11" t="n">
         <v>0.8692</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.7084</v>
+        <v>-12.7734</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.591500000000001</v>
+        <v>-3.6563</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.116999999999999</v>
+        <v>-9.116900000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-9.3521</v>
@@ -1390,13 +1390,13 @@
         <v>14.8789</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9919999999999995</v>
+        <v>1.9272</v>
       </c>
       <c r="T12" t="n">
-        <v>1.984600000000001</v>
+        <v>2.9199</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9923999999999999</v>
+        <v>-0.9925999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0.6032000000000004</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.0645</v>
+        <v>5.5806</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0434</v>
+        <v>4.4515</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0212</v>
+        <v>1.1291</v>
       </c>
       <c r="G13" t="n">
         <v>3.3706</v>
@@ -1468,13 +1468,13 @@
         <v>3.1741</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7499</v>
+        <v>-0.2338</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4307</v>
+        <v>-0.0226</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3192</v>
+        <v>-0.2112</v>
       </c>
       <c r="V13" t="n">
         <v>-0.532</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. CASTILLO EDIO</t>
+          <t>L. MARTINEZ YRANZO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0969</v>
+        <v>3.0961</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6173</v>
+        <v>2.2575</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4796</v>
+        <v>0.8386</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2256</v>
+        <v>1.15</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7411</v>
+        <v>0.8468</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4845</v>
+        <v>0.3032</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1913</v>
+        <v>1.9862</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4607</v>
+        <v>1.3009</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7306</v>
+        <v>0.6853</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.9657</v>
+        <v>-0.8363</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.7197</v>
+        <v>-0.4542</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2461</v>
+        <v>-0.3821</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3968</v>
+        <v>1.5871</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.1741</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.5709</v>
+        <v>1.5871</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2681</v>
+        <v>-0.1729</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1872</v>
+        <v>-0.2607</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0809</v>
+        <v>0.0878</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2065</v>
+        <v>0.532</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4129</v>
+        <v>0.532</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. MARTINEZ YRANZO</t>
+          <t>A. CASTILLO EDIO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6285</v>
+        <v>3.0145</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6454</v>
+        <v>2.5152</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9831</v>
+        <v>0.4992</v>
       </c>
       <c r="G15" t="n">
-        <v>1.15</v>
+        <v>1.2256</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8468</v>
+        <v>0.7411</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3032</v>
+        <v>0.4845</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9862</v>
+        <v>3.1913</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3009</v>
+        <v>2.4607</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6853</v>
+        <v>0.7306</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8363</v>
+        <v>-1.9657</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4542</v>
+        <v>-1.7197</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3821</v>
+        <v>-0.2461</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5871</v>
+        <v>0.3968</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.1741</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5871</v>
+        <v>3.5709</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6405</v>
+        <v>0.1856</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8728</v>
+        <v>0.0852</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2323</v>
+        <v>0.1005</v>
       </c>
       <c r="V15" t="n">
-        <v>0.532</v>
+        <v>1.2065</v>
       </c>
       <c r="W15" t="n">
-        <v>0.532</v>
+        <v>2.4129</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. CEBRIA PUCHADES</t>
+          <t>J. ROSA DE SOUSA DA SILVA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5645</v>
+        <v>1.9613</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5652</v>
+        <v>0.9962</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9993</v>
+        <v>0.9651</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9033</v>
+        <v>0.6473</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4936</v>
+        <v>-1.0989</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4097</v>
+        <v>1.7462</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2182</v>
+        <v>1.3475</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6855</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5327</v>
+        <v>2.2644</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3149</v>
+        <v>-0.7002</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1918</v>
+        <v>-0.1821</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.123</v>
+        <v>-0.5182</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.9838</v>
+        <v>1.9838</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.9677</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>1.9838</v>
       </c>
       <c r="S16" t="n">
-        <v>0.645</v>
+        <v>-0.4038</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0487</v>
+        <v>-0.3513</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4036</v>
+        <v>-0.0525</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
       <c r="W16" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>-0.266</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ROSA DE SOUSA DA SILVA</t>
+          <t>V. CEBRIA PUCHADES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0949</v>
+        <v>0.8401</v>
       </c>
       <c r="E17" t="n">
-        <v>0.486</v>
+        <v>-0.047</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6089</v>
+        <v>0.8871</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6473</v>
+        <v>2.9033</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0989</v>
+        <v>0.4936</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7462</v>
+        <v>2.4097</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3475</v>
+        <v>3.2182</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.9167999999999999</v>
+        <v>0.6855</v>
       </c>
       <c r="L17" t="n">
-        <v>2.2644</v>
+        <v>2.5327</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7002</v>
+        <v>-0.3149</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1821</v>
+        <v>-0.1918</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5182</v>
+        <v>-0.123</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9838</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.9677</v>
       </c>
       <c r="R17" t="n">
         <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2702</v>
+        <v>-0.0794</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8615</v>
+        <v>0.4365</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4088</v>
+        <v>-0.5159</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X17" t="n">
         <v>-0.266</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. PIQUERAS CARBONELL</t>
+          <t>D. MARTIN VELA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5483</v>
+        <v>0.7022</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.2216</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5483</v>
+        <v>0.4806</v>
       </c>
       <c r="G18" t="n">
-        <v>0.07049999999999999</v>
+        <v>-0.2699</v>
       </c>
       <c r="H18" t="n">
-        <v>0.07049999999999999</v>
+        <v>-0.3126</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.0427</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.0629</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.0202</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.0427</v>
       </c>
       <c r="M18" t="n">
-        <v>0.07049999999999999</v>
+        <v>-0.3328</v>
       </c>
       <c r="N18" t="n">
-        <v>0.07049999999999999</v>
+        <v>-0.3328</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3968</v>
+        <v>0.9919</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3968</v>
+        <v>0.9919</v>
       </c>
       <c r="S18" t="n">
-        <v>0.081</v>
+        <v>-0.0198</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.1587</v>
       </c>
       <c r="U18" t="n">
-        <v>0.081</v>
+        <v>-0.1786</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5483</v>
+        <v>0.5763</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5483</v>
+        <v>0.5763</v>
       </c>
       <c r="G19" t="n">
         <v>0.07049999999999999</v>
@@ -1936,13 +1936,13 @@
         <v>0.3968</v>
       </c>
       <c r="S19" t="n">
-        <v>0.081</v>
+        <v>0.1091</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.081</v>
+        <v>0.1091</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5483</v>
+        <v>0.5763</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5483</v>
+        <v>0.5763</v>
       </c>
       <c r="G20" t="n">
         <v>0.07049999999999999</v>
@@ -2014,13 +2014,13 @@
         <v>0.3968</v>
       </c>
       <c r="S20" t="n">
-        <v>0.081</v>
+        <v>0.1091</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.081</v>
+        <v>0.1091</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. NDIAYE</t>
+          <t>A. PIQUERAS CARBONELL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3895</v>
+        <v>0.5763</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3654</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9759</v>
+        <v>0.5763</v>
       </c>
       <c r="G21" t="n">
-        <v>0.625</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4941</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1309</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8645</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1.6235</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.241</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2395</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1295</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3968</v>
+        <v>0.3968</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1822</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7855</v>
+        <v>0.3968</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3677</v>
+        <v>0.1091</v>
       </c>
       <c r="T21" t="n">
-        <v>1.4171</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0494</v>
+        <v>0.1091</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. MARTIN VELA</t>
+          <t>H. RAMON AÑIBARRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.238</v>
+        <v>-0.1482</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1865</v>
+        <v>0.3964</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4245</v>
+        <v>-0.5446</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2699</v>
+        <v>1.548</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3126</v>
+        <v>-0.6454</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0427</v>
+        <v>2.1933</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0629</v>
+        <v>2.3988</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0202</v>
+        <v>0.348</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0427</v>
+        <v>2.0508</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3328</v>
+        <v>-0.8509</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3328</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.1425</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9919</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-4.1661</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9919</v>
+        <v>2.579</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4841</v>
+        <v>0.2282</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2494</v>
+        <v>0.4252</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2347</v>
+        <v>-0.197</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.7384</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>H. RAMON AÑIBARRO</t>
+          <t>L. NDIAYE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0266</v>
+        <v>-0.2626</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9065</v>
+        <v>0.5491</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9331</v>
+        <v>-0.8118</v>
       </c>
       <c r="G23" t="n">
-        <v>1.548</v>
+        <v>0.625</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6454</v>
+        <v>0.4941</v>
       </c>
       <c r="I23" t="n">
-        <v>2.1933</v>
+        <v>0.1309</v>
       </c>
       <c r="J23" t="n">
-        <v>2.3988</v>
+        <v>1.8645</v>
       </c>
       <c r="K23" t="n">
-        <v>0.348</v>
+        <v>1.6235</v>
       </c>
       <c r="L23" t="n">
-        <v>2.0508</v>
+        <v>0.241</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8509</v>
+        <v>-1.2395</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-1.1295</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1425</v>
+        <v>-0.11</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5871</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.1661</v>
+        <v>-2.1822</v>
       </c>
       <c r="R23" t="n">
-        <v>2.579</v>
+        <v>1.7855</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3498</v>
+        <v>0.7156</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9353</v>
+        <v>0.6009</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5856</v>
+        <v>0.1147</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3373</v>
+        <v>-1.2065</v>
       </c>
       <c r="W23" t="n">
-        <v>1.7384</v>
+        <v>0.266</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.0757</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9866</v>
+        <v>-1.4441</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3256</v>
+        <v>-2.2236</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3391</v>
+        <v>0.7795</v>
       </c>
       <c r="G24" t="n">
         <v>-2.0591</v>
@@ -2326,13 +2326,13 @@
         <v>1.9838</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.721</v>
+        <v>-0.1785</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1813</v>
+        <v>-0.0793</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5397</v>
+        <v>-0.0993</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>13.7085</v>
+        <v>15.0688</v>
       </c>
       <c r="E25" t="n">
-        <v>9.117099999999999</v>
+        <v>9.116899999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>4.5916</v>
+        <v>5.9517</v>
       </c>
       <c r="G25" t="n">
         <v>9.3523</v>
@@ -2380,7 +2380,7 @@
         <v>17.7877</v>
       </c>
       <c r="K25" t="n">
-        <v>5.9018</v>
+        <v>5.901800000000001</v>
       </c>
       <c r="L25" t="n">
         <v>11.886</v>
@@ -2389,13 +2389,13 @@
         <v>-8.435700000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.2379</v>
+        <v>-7.237900000000001</v>
       </c>
       <c r="O25" t="n">
         <v>-1.1979</v>
       </c>
       <c r="P25" t="n">
-        <v>5.951600000000001</v>
+        <v>5.9516</v>
       </c>
       <c r="Q25" t="n">
         <v>-14.8788</v>
@@ -2404,13 +2404,13 @@
         <v>20.8303</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9921000000000002</v>
+        <v>0.3684999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>0.9925999999999999</v>
+        <v>0.9925999999999998</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.9848</v>
+        <v>-0.6241999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6032999999999999</v>
